--- a/KahootBlank.xlsx
+++ b/KahootBlank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zaeem\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E542724C-497A-4143-8774-DE0B9BA1A808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828412E0-E604-4F64-B953-F0E23CA332D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,19 +58,19 @@
     <t>Correct answer(s) - choose at least one</t>
   </si>
   <si>
-    <t>In a Grade/Maven based project, where do test resources go.</t>
+    <t>What is a Java interface primarily used for?</t>
   </si>
   <si>
-    <t>src/main/java</t>
+    <t>An abstract definition of a class that lists several methods/fields.</t>
   </si>
   <si>
-    <t>src/test/java</t>
+    <t>To store state information within a class.</t>
   </si>
   <si>
-    <t>src/test/resources</t>
+    <t>To automatically generate method implementations.</t>
   </si>
   <si>
-    <t>src/main/resources</t>
+    <t>To automatically generate method implementations based on the class's attributes and predefined logic.</t>
   </si>
 </sst>
 </file>
@@ -244,77 +244,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <sz val="10"/>
@@ -1091,7 +1021,7 @@
       <c r="Z7" s="12"/>
       <c r="AA7" s="12"/>
     </row>
-    <row r="8" spans="1:27" ht="48.75" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" ht="56.25" x14ac:dyDescent="0.35">
       <c r="A8" s="11"/>
       <c r="B8" s="13" t="s">
         <v>5</v>
@@ -1142,19 +1072,19 @@
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="14">
-        <v>60</v>
+      <c r="G9" s="15">
+        <v>10</v>
       </c>
       <c r="H9" s="15">
         <v>3</v>
@@ -4997,18 +4927,18 @@
     <mergeCell ref="B6:H6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19:B107">
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>LEN(B19)&gt;120</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:F107">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>LEN(C19)&gt;75</formula>
+  <conditionalFormatting sqref="B9:H9">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>LEN(B9)&gt;120</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9:H9">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>LEN(B9)&gt;120</formula>
+  <conditionalFormatting sqref="C19:F107">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>LEN(C19)&gt;75</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
